--- a/output/tepra/2026/Tepra Kobar_Progres PBJ tahun 2026 (2026-08-03).xlsx
+++ b/output/tepra/2026/Tepra Kobar_Progres PBJ tahun 2026 (2026-08-03).xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -701,10 +701,10 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>291008487</v>
+        <v>4500000</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>291008487</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>317493140</v>
+        <v>19500000</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>1</v>
@@ -760,11 +760,15 @@
       <c r="H10" s="10" t="n">
         <v>19500000</v>
       </c>
-      <c r="I10" s="8" t="n">
-        <v>71</v>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v>297993140</v>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
@@ -776,11 +780,15 @@
           <t>Badan Keuangan dan Aset Daerah</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>92</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>694885745</v>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -802,11 +810,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="4" t="n">
-        <v>92</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>694885745</v>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
@@ -819,10 +831,10 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>93</v>
+        <v>2</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>494143453</v>
+        <v>19928718</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>2</v>
@@ -836,11 +848,15 @@
       <c r="H12" s="10" t="n">
         <v>16692513</v>
       </c>
-      <c r="I12" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="J12" s="10" t="n">
-        <v>474214735</v>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="45" customHeight="1">
@@ -853,10 +869,10 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>732115182</v>
+        <v>169489998</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>5</v>
@@ -870,11 +886,15 @@
       <c r="H13" s="6" t="n">
         <v>164526300</v>
       </c>
-      <c r="I13" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>562625184</v>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
@@ -887,10 +907,10 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>125</v>
+        <v>2</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>777986001</v>
+        <v>63250745</v>
       </c>
       <c r="E14" s="8" t="n">
         <v>2</v>
@@ -904,11 +924,15 @@
       <c r="H14" s="10" t="n">
         <v>62335938</v>
       </c>
-      <c r="I14" s="8" t="n">
-        <v>123</v>
-      </c>
-      <c r="J14" s="10" t="n">
-        <v>714735256</v>
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
@@ -921,10 +945,10 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>837899282</v>
+        <v>53461794</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>4</v>
@@ -938,11 +962,15 @@
       <c r="H15" s="6" t="n">
         <v>53392478</v>
       </c>
-      <c r="I15" s="4" t="n">
-        <v>78</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>784437488</v>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
@@ -955,10 +983,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>491911485</v>
+        <v>84108354</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>4</v>
@@ -972,11 +1000,15 @@
       <c r="H16" s="10" t="n">
         <v>78149208</v>
       </c>
-      <c r="I16" s="8" t="n">
-        <v>73</v>
-      </c>
-      <c r="J16" s="10" t="n">
-        <v>407803131</v>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1">
@@ -989,10 +1021,10 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>677290237</v>
+        <v>137583844</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>13</v>
@@ -1006,11 +1038,15 @@
       <c r="H17" s="6" t="n">
         <v>116218702</v>
       </c>
-      <c r="I17" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>539706393</v>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1">
@@ -1023,10 +1059,10 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>553370393</v>
+        <v>350423349</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>17</v>
@@ -1040,11 +1076,15 @@
       <c r="H18" s="10" t="n">
         <v>350174900</v>
       </c>
-      <c r="I18" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="J18" s="10" t="n">
-        <v>202947044</v>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
@@ -1057,10 +1097,10 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>127</v>
+        <v>33</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>908204422</v>
+        <v>278259519</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>33</v>
@@ -1074,11 +1114,15 @@
       <c r="H19" s="6" t="n">
         <v>258444643</v>
       </c>
-      <c r="I19" s="4" t="n">
-        <v>94</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>629944903</v>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="45" customHeight="1">
@@ -1091,10 +1135,10 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>780728426</v>
+        <v>38508000</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>1</v>
@@ -1108,11 +1152,15 @@
       <c r="H20" s="10" t="n">
         <v>38508000</v>
       </c>
-      <c r="I20" s="8" t="n">
-        <v>96</v>
-      </c>
-      <c r="J20" s="10" t="n">
-        <v>742220426</v>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1">
@@ -1125,10 +1173,10 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>164</v>
+        <v>54</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2090003236</v>
+        <v>1163796564</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>52</v>
@@ -1143,10 +1191,10 @@
         <v>1095681550.6</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>112</v>
+        <v>2</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>973878876</v>
+        <v>47672204</v>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
@@ -1159,10 +1207,10 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>444206345</v>
+        <v>32101092</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>5</v>
@@ -1176,11 +1224,15 @@
       <c r="H22" s="10" t="n">
         <v>29240607</v>
       </c>
-      <c r="I22" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="J22" s="10" t="n">
-        <v>412105253</v>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1">
@@ -1193,10 +1245,10 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>342136823</v>
+        <v>30262050</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>5</v>
@@ -1210,11 +1262,15 @@
       <c r="H23" s="6" t="n">
         <v>26778260</v>
       </c>
-      <c r="I23" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>311874773</v>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1">
@@ -1227,10 +1283,10 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>120</v>
+        <v>4</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>775509241</v>
+        <v>81327566</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>4</v>
@@ -1244,11 +1300,15 @@
       <c r="H24" s="10" t="n">
         <v>75876500</v>
       </c>
-      <c r="I24" s="8" t="n">
-        <v>116</v>
-      </c>
-      <c r="J24" s="10" t="n">
-        <v>694181675</v>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
@@ -1261,10 +1321,10 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>304521329</v>
+        <v>98994684</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>4</v>
@@ -1278,11 +1338,15 @@
       <c r="H25" s="6" t="n">
         <v>51881289</v>
       </c>
-      <c r="I25" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="J25" s="6" t="n">
-        <v>205526645</v>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
@@ -1295,10 +1359,10 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>234</v>
+        <v>48</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>2238310494</v>
+        <v>535240106</v>
       </c>
       <c r="E26" s="8" t="n">
         <v>30</v>
@@ -1313,10 +1377,10 @@
         <v>272586367</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>1963250696</v>
+        <v>260180308</v>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1">
@@ -1329,10 +1393,10 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>418455903</v>
+        <v>93366423</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>6</v>
@@ -1346,11 +1410,15 @@
       <c r="H27" s="6" t="n">
         <v>92923430</v>
       </c>
-      <c r="I27" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="J27" s="6" t="n">
-        <v>325089480</v>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
@@ -1363,10 +1431,10 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>859678273</v>
+        <v>334343818</v>
       </c>
       <c r="E28" s="8" t="n">
         <v>13</v>
@@ -1380,11 +1448,15 @@
       <c r="H28" s="10" t="n">
         <v>330804697</v>
       </c>
-      <c r="I28" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="J28" s="10" t="n">
-        <v>525334455</v>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="45" customHeight="1">
@@ -1397,10 +1469,10 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>858385693</v>
+        <v>318496502</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>13</v>
@@ -1414,11 +1486,15 @@
       <c r="H29" s="6" t="n">
         <v>312310710</v>
       </c>
-      <c r="I29" s="4" t="n">
-        <v>82</v>
-      </c>
-      <c r="J29" s="6" t="n">
-        <v>539889191</v>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
@@ -1431,10 +1507,10 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>342405479</v>
+        <v>76153486</v>
       </c>
       <c r="E30" s="8" t="n">
         <v>7</v>
@@ -1448,11 +1524,15 @@
       <c r="H30" s="10" t="n">
         <v>67861324</v>
       </c>
-      <c r="I30" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="J30" s="10" t="n">
-        <v>266251993</v>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="45" customHeight="1">
@@ -1465,10 +1545,10 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>1305525621</v>
+        <v>280944208</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>10</v>
@@ -1482,11 +1562,15 @@
       <c r="H31" s="6" t="n">
         <v>277956656</v>
       </c>
-      <c r="I31" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="J31" s="6" t="n">
-        <v>1024581413</v>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
@@ -1499,10 +1583,10 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>880998213</v>
+        <v>531595655</v>
       </c>
       <c r="E32" s="8" t="n">
         <v>22</v>
@@ -1517,10 +1601,10 @@
         <v>440947598</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>362815243</v>
+        <v>13412685</v>
       </c>
     </row>
     <row r="33" ht="45" customHeight="1">
@@ -1533,10 +1617,10 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>744929925</v>
+        <v>69841346</v>
       </c>
       <c r="E33" s="4" t="n">
         <v>13</v>
@@ -1550,11 +1634,15 @@
       <c r="H33" s="6" t="n">
         <v>63527950</v>
       </c>
-      <c r="I33" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="J33" s="6" t="n">
-        <v>675088579</v>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="45" customHeight="1">
@@ -1567,10 +1655,10 @@
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>87</v>
+        <v>6</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>550936395</v>
+        <v>73983300</v>
       </c>
       <c r="E34" s="8" t="n">
         <v>6</v>
@@ -1584,11 +1672,15 @@
       <c r="H34" s="10" t="n">
         <v>73788167</v>
       </c>
-      <c r="I34" s="8" t="n">
-        <v>81</v>
-      </c>
-      <c r="J34" s="10" t="n">
-        <v>476953095</v>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="45" customHeight="1">
@@ -1601,10 +1693,10 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>476139500</v>
+        <v>12917292</v>
       </c>
       <c r="E35" s="4" t="n">
         <v>1</v>
@@ -1618,11 +1710,15 @@
       <c r="H35" s="6" t="n">
         <v>11908080</v>
       </c>
-      <c r="I35" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="J35" s="6" t="n">
-        <v>463222208</v>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="45" customHeight="1">
@@ -1635,10 +1731,10 @@
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>251691298</v>
+        <v>94995000</v>
       </c>
       <c r="E36" s="8" t="n">
         <v>3</v>
@@ -1652,11 +1748,15 @@
       <c r="H36" s="10" t="n">
         <v>23225929</v>
       </c>
-      <c r="I36" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="J36" s="10" t="n">
-        <v>156696298</v>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="45" customHeight="1">
@@ -1669,10 +1769,10 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>173</v>
+        <v>11</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>1076116871</v>
+        <v>209482901</v>
       </c>
       <c r="E37" s="4" t="n">
         <v>9</v>
@@ -1687,10 +1787,10 @@
         <v>111937628</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>164</v>
+        <v>2</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>961393970</v>
+        <v>94760000</v>
       </c>
     </row>
     <row r="38" ht="45" customHeight="1">
@@ -1699,14 +1799,18 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Arut Utara</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>310252566</v>
+          <t>Kecamatan Kotawaringin Lama</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
@@ -1728,11 +1832,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="J38" s="10" t="n">
-        <v>310252566</v>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="45" customHeight="1">
@@ -1741,40 +1849,32 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Kotawaringin Lama</t>
+          <t>Kecamatan Kumai</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>382528466</v>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>186980127</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>152171825</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>145682100</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>382528466</v>
+        <v>34808302</v>
       </c>
     </row>
     <row r="40" ht="45" customHeight="1">
@@ -1783,32 +1883,48 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Kumai</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="n">
-        <v>109</v>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>622521476</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="F40" s="10" t="n">
-        <v>152171825</v>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="H40" s="10" t="n">
-        <v>145682100</v>
-      </c>
-      <c r="I40" s="8" t="n">
-        <v>98</v>
-      </c>
-      <c r="J40" s="10" t="n">
-        <v>470349651</v>
+          <t>Kecamatan Pangkalan Banteng</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="45" customHeight="1">
@@ -1817,14 +1933,14 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Banteng</t>
+          <t>Laboratorium Kesehatan Daerah</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>175284644</v>
+        <v>31600000</v>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
@@ -1847,10 +1963,10 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>175284644</v>
+        <v>31600000</v>
       </c>
     </row>
     <row r="42" ht="45" customHeight="1">
@@ -1859,14 +1975,14 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Lada</t>
+          <t>Puskesmas Arut Selatan</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>219851775</v>
+        <v>21000000</v>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
@@ -1889,10 +2005,10 @@
         </is>
       </c>
       <c r="I42" s="8" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>219851775</v>
+        <v>21000000</v>
       </c>
     </row>
     <row r="43" ht="45" customHeight="1">
@@ -1901,14 +2017,18 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Laboratorium Kesehatan Daerah</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="D43" s="6" t="n">
-        <v>166377553</v>
+          <t>Puskesmas Natai Pelingkau</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
@@ -1930,11 +2050,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="J43" s="6" t="n">
-        <v>166377553</v>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44" ht="45" customHeight="1">
@@ -1943,40 +2067,36 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Selatan</t>
+          <t>Puskesmas Riam Durian</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>463616007</v>
-      </c>
-      <c r="E44" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F44" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G44" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H44" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I44" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="J44" s="10" t="n">
-        <v>463616007</v>
+        <v>66380633</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>66380633</v>
+      </c>
+      <c r="G44" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H44" s="10" t="n">
+        <v>15724250</v>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="45" customHeight="1">
@@ -1985,40 +2105,36 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Utara</t>
+          <t>Rumah Sakit Kutaringin</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>51896600</v>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I45" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J45" s="6" t="n">
-        <v>51896600</v>
+        <v>35716900</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>35716900</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>26129400</v>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="46" ht="45" customHeight="1">
@@ -2027,14 +2143,18 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Ipuh Bangun Jaya</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="D46" s="10" t="n">
-        <v>183754320</v>
+          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
@@ -2056,11 +2176,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="J46" s="10" t="n">
-        <v>183754320</v>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="47" ht="45" customHeight="1">
@@ -2069,40 +2193,32 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Karang Mulya</t>
+          <t>Satuan Polisi Pamong Praja</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>489429711</v>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>129198291</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>119763291</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>118233150</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>489429711</v>
+        <v>9435000</v>
       </c>
     </row>
     <row r="48" ht="45" customHeight="1">
@@ -2111,40 +2227,36 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Kotawaringin Lama</t>
+          <t>Sekretariat DPRD</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>162372837</v>
-      </c>
-      <c r="E48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I48" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="J48" s="10" t="n">
-        <v>162372837</v>
+        <v>401182597</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>401182597</v>
+      </c>
+      <c r="G48" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="H48" s="10" t="n">
+        <v>395443026</v>
+      </c>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="49" ht="45" customHeight="1">
@@ -2153,746 +2265,68 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Kumai</t>
+          <t>Sekretariat Daerah</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>397703689</v>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="J49" s="6" t="n">
-        <v>397703689</v>
+        <v>183633343</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>183633343</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>160778238</v>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50" ht="45" customHeight="1">
-      <c r="A50" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Kumpai Batu Atas</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="n">
-        <v>41</v>
-      </c>
-      <c r="D50" s="10" t="n">
-        <v>319912312</v>
-      </c>
-      <c r="E50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I50" s="8" t="n">
-        <v>41</v>
-      </c>
-      <c r="J50" s="10" t="n">
-        <v>319912312</v>
-      </c>
-    </row>
-    <row r="51" ht="45" customHeight="1">
-      <c r="A51" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Madurejo</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="D51" s="6" t="n">
-        <v>138079030</v>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="J51" s="6" t="n">
-        <v>138079030</v>
-      </c>
-    </row>
-    <row r="52" ht="45" customHeight="1">
-      <c r="A52" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Mendawai</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="D52" s="10" t="n">
-        <v>411198562</v>
-      </c>
-      <c r="E52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I52" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="J52" s="10" t="n">
-        <v>411198562</v>
-      </c>
-    </row>
-    <row r="53" ht="45" customHeight="1">
-      <c r="A53" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Natai Pelingkau</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="D53" s="6" t="n">
-        <v>387164122</v>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I53" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="J53" s="6" t="n">
-        <v>387164122</v>
-      </c>
-    </row>
-    <row r="54" ht="45" customHeight="1">
-      <c r="A54" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Pandu Sanjaya</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="D54" s="10" t="n">
-        <v>289499767</v>
-      </c>
-      <c r="E54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I54" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="J54" s="10" t="n">
-        <v>289499767</v>
-      </c>
-    </row>
-    <row r="55" ht="45" customHeight="1">
-      <c r="A55" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Pangkalan Lada</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="D55" s="6" t="n">
-        <v>240267455</v>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="J55" s="6" t="n">
-        <v>240267455</v>
-      </c>
-    </row>
-    <row r="56" ht="45" customHeight="1">
-      <c r="A56" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Riam Durian</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="D56" s="10" t="n">
-        <v>153251633</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="F56" s="10" t="n">
-        <v>66380633</v>
-      </c>
-      <c r="G56" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="H56" s="10" t="n">
-        <v>15724250</v>
-      </c>
-      <c r="I56" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="J56" s="10" t="n">
-        <v>86871000</v>
-      </c>
-    </row>
-    <row r="57" ht="45" customHeight="1">
-      <c r="A57" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Runtu</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="D57" s="6" t="n">
-        <v>186180796</v>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I57" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="J57" s="6" t="n">
-        <v>186180796</v>
-      </c>
-    </row>
-    <row r="58" ht="45" customHeight="1">
-      <c r="A58" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Sambi</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="D58" s="10" t="n">
-        <v>121367900</v>
-      </c>
-      <c r="E58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I58" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="J58" s="10" t="n">
-        <v>121367900</v>
-      </c>
-    </row>
-    <row r="59" ht="45" customHeight="1">
-      <c r="A59" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Semanggang</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="D59" s="6" t="n">
-        <v>378945500</v>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="J59" s="6" t="n">
-        <v>378945500</v>
-      </c>
-    </row>
-    <row r="60" ht="45" customHeight="1">
-      <c r="A60" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Sungai Rangit</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="D60" s="10" t="n">
-        <v>382606656</v>
-      </c>
-      <c r="E60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I60" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="J60" s="10" t="n">
-        <v>382606656</v>
-      </c>
-    </row>
-    <row r="61" ht="45" customHeight="1">
-      <c r="A61" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Teluk Bogam</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D61" s="6" t="n">
-        <v>193865001</v>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I61" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="J61" s="6" t="n">
-        <v>193865001</v>
-      </c>
-    </row>
-    <row r="62" ht="45" customHeight="1">
-      <c r="A62" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Kutaringin</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="D62" s="10" t="n">
-        <v>345486342</v>
-      </c>
-      <c r="E62" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F62" s="10" t="n">
-        <v>35716900</v>
-      </c>
-      <c r="G62" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H62" s="10" t="n">
-        <v>26129400</v>
-      </c>
-      <c r="I62" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="J62" s="10" t="n">
-        <v>309769442</v>
-      </c>
-    </row>
-    <row r="63" ht="45" customHeight="1">
-      <c r="A63" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="D63" s="6" t="n">
-        <v>575029667</v>
-      </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I63" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="J63" s="6" t="n">
-        <v>575029667</v>
-      </c>
-    </row>
-    <row r="64" ht="45" customHeight="1">
-      <c r="A64" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>Satuan Polisi Pamong Praja</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="D64" s="10" t="n">
-        <v>354293991</v>
-      </c>
-      <c r="E64" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F64" s="10" t="n">
-        <v>119763291</v>
-      </c>
-      <c r="G64" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H64" s="10" t="n">
-        <v>118233150</v>
-      </c>
-      <c r="I64" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="J64" s="10" t="n">
-        <v>234530700</v>
-      </c>
-    </row>
-    <row r="65" ht="45" customHeight="1">
-      <c r="A65" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>Sekretariat DPRD</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>106</v>
-      </c>
-      <c r="D65" s="6" t="n">
-        <v>1314919871</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="F65" s="6" t="n">
-        <v>401182597</v>
-      </c>
-      <c r="G65" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="H65" s="6" t="n">
-        <v>395443026</v>
-      </c>
-      <c r="I65" s="4" t="n">
-        <v>89</v>
-      </c>
-      <c r="J65" s="6" t="n">
-        <v>913737274</v>
-      </c>
-    </row>
-    <row r="66" ht="45" customHeight="1">
-      <c r="A66" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>Sekretariat Daerah</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="n">
-        <v>147</v>
-      </c>
-      <c r="D66" s="10" t="n">
-        <v>1352438071</v>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="F66" s="10" t="n">
-        <v>183633343</v>
-      </c>
-      <c r="G66" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="H66" s="10" t="n">
-        <v>160778238</v>
-      </c>
-      <c r="I66" s="8" t="n">
-        <v>127</v>
-      </c>
-      <c r="J66" s="10" t="n">
-        <v>1168804728</v>
-      </c>
-    </row>
-    <row r="67" ht="45" customHeight="1">
-      <c r="A67" s="2" t="inlineStr"/>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>TOTAL KESELURUHAN</t>
         </is>
       </c>
-      <c r="C67" s="12" t="n">
-        <v>3880</v>
-      </c>
-      <c r="D67" s="13" t="n">
-        <v>32287083212</v>
-      </c>
-      <c r="E67" s="12" t="n">
+      <c r="C50" s="12" t="n">
+        <v>386</v>
+      </c>
+      <c r="D50" s="13" t="n">
+        <v>6312548205</v>
+      </c>
+      <c r="E50" s="12" t="n">
         <v>353</v>
       </c>
-      <c r="F67" s="13" t="n">
+      <c r="F50" s="13" t="n">
         <v>5795179706</v>
       </c>
-      <c r="G67" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>353</v>
       </c>
-      <c r="H67" s="13" t="n">
+      <c r="H50" s="13" t="n">
         <v>5379169588.6</v>
       </c>
-      <c r="I67" s="12" t="n">
-        <v>3527</v>
-      </c>
-      <c r="J67" s="13" t="n">
-        <v>26491903506</v>
+      <c r="I50" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="J50" s="13" t="n">
+        <v>517368499</v>
       </c>
     </row>
   </sheetData>
@@ -2924,7 +2358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3194,10 +2628,10 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>259388320</v>
+        <v>59000000</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -3240,10 +2674,10 @@
         </is>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>259388320</v>
+        <v>59000000</v>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
@@ -3256,10 +2690,10 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>513247490</v>
+        <v>190310330</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>2</v>
@@ -3289,11 +2723,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M10" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N10" s="10" t="n">
-        <v>322937160</v>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
@@ -3306,10 +2744,10 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>484082242</v>
+        <v>168902040</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>1</v>
@@ -3339,11 +2777,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M11" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>315180202</v>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
@@ -3356,10 +2798,10 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>869448547</v>
+        <v>439139830</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>4</v>
@@ -3385,11 +2827,15 @@
       <c r="L12" s="10" t="n">
         <v>57714450</v>
       </c>
-      <c r="M12" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="N12" s="10" t="n">
-        <v>430308717</v>
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="45" customHeight="1">
@@ -3402,10 +2848,10 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1559854479</v>
+        <v>817935443</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>5</v>
@@ -3436,10 +2882,10 @@
         </is>
       </c>
       <c r="M13" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>1049541276</v>
+        <v>307622240</v>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
@@ -3505,11 +2951,15 @@
           <t>Dinas Kepemudaan dan Olahraga</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>957216782</v>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -3551,11 +3001,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M15" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="N15" s="6" t="n">
-        <v>957216782</v>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
@@ -3568,10 +3022,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>266301572</v>
+        <v>54773006</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>1</v>
@@ -3601,11 +3055,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M16" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="N16" s="10" t="n">
-        <v>211528566</v>
+      <c r="M16" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1">
@@ -3618,10 +3076,10 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1566751699</v>
+        <v>1225542538</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>10</v>
@@ -3648,10 +3106,10 @@
         <v>237557765</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>471393957</v>
+        <v>130184796</v>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1">
@@ -3664,10 +3122,10 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>1109929988</v>
+        <v>873381088</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>11</v>
@@ -3693,11 +3151,15 @@
       <c r="L18" s="10" t="n">
         <v>55664280</v>
       </c>
-      <c r="M18" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N18" s="10" t="n">
-        <v>236548900</v>
+      <c r="M18" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
@@ -3710,10 +3172,10 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1888168641</v>
+        <v>905090000</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>6</v>
@@ -3739,11 +3201,15 @@
       <c r="L19" s="6" t="n">
         <v>194832750</v>
       </c>
-      <c r="M19" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="N19" s="6" t="n">
-        <v>983078641</v>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="45" customHeight="1">
@@ -3756,10 +3222,10 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>1467806996</v>
+        <v>429952000</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>3</v>
@@ -3789,11 +3255,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M20" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="N20" s="10" t="n">
-        <v>1037854996</v>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1">
@@ -3806,10 +3276,10 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>19684340479</v>
+        <v>17216344778</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>122</v>
@@ -3835,11 +3305,15 @@
       <c r="L21" s="6" t="n">
         <v>72965295</v>
       </c>
-      <c r="M21" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="N21" s="6" t="n">
-        <v>2467995701</v>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
@@ -3852,10 +3326,10 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>376694000</v>
+        <v>288750000</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>2</v>
@@ -3885,11 +3359,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M22" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" s="10" t="n">
-        <v>87944000</v>
+      <c r="M22" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1">
@@ -3902,10 +3380,10 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>405798874</v>
+        <v>66310000</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>1</v>
@@ -3935,11 +3413,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M23" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>339488874</v>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1">
@@ -3952,10 +3434,10 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>610038436</v>
+        <v>146351500</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>2</v>
@@ -3985,11 +3467,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M24" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="N24" s="10" t="n">
-        <v>463686936</v>
+      <c r="M24" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
@@ -4056,10 +3542,10 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>6408513766</v>
+        <v>4014437462</v>
       </c>
       <c r="E26" s="8" t="n">
         <v>24</v>
@@ -4090,10 +3576,10 @@
         </is>
       </c>
       <c r="M26" s="8" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="N26" s="10" t="n">
-        <v>3430812569</v>
+        <v>1036736265</v>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1">
@@ -4106,10 +3592,10 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>1177904322</v>
+        <v>913021368</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>7</v>
@@ -4139,11 +3625,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M27" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N27" s="6" t="n">
-        <v>264882954</v>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
@@ -4156,10 +3646,10 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>5044708697</v>
+        <v>3344224943</v>
       </c>
       <c r="E28" s="8" t="n">
         <v>24</v>
@@ -4190,10 +3680,10 @@
         </is>
       </c>
       <c r="M28" s="8" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="N28" s="10" t="n">
-        <v>1822466094</v>
+        <v>121982340</v>
       </c>
     </row>
     <row r="29" ht="45" customHeight="1">
@@ -4206,10 +3696,10 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>2784104510</v>
+        <v>1079232601</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>11</v>
@@ -4235,11 +3725,15 @@
       <c r="L29" s="6" t="n">
         <v>50500763</v>
       </c>
-      <c r="M29" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="N29" s="6" t="n">
-        <v>1704871909</v>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
@@ -4251,11 +3745,15 @@
           <t>Dinas Perpustakaan dan Kearsipan</t>
         </is>
       </c>
-      <c r="C30" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>190561024</v>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
@@ -4297,11 +3795,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M30" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="N30" s="10" t="n">
-        <v>190561024</v>
+      <c r="M30" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="45" customHeight="1">
@@ -4314,10 +3816,10 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>4842583639</v>
+        <v>2428743641</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>20</v>
@@ -4343,11 +3845,15 @@
       <c r="L31" s="6" t="n">
         <v>94888350</v>
       </c>
-      <c r="M31" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="N31" s="6" t="n">
-        <v>2413839998</v>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
@@ -4360,10 +3866,10 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>24100076698</v>
+        <v>22919967978</v>
       </c>
       <c r="E32" s="8" t="n">
         <v>132</v>
@@ -4394,10 +3900,10 @@
         </is>
       </c>
       <c r="M32" s="8" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="N32" s="10" t="n">
-        <v>6764951620</v>
+        <v>5584842900</v>
       </c>
     </row>
     <row r="33" ht="45" customHeight="1">
@@ -4409,11 +3915,15 @@
           <t>Dinas Sosial</t>
         </is>
       </c>
-      <c r="C33" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>1113387305</v>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
@@ -4455,11 +3965,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M33" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="N33" s="6" t="n">
-        <v>1113387305</v>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="45" customHeight="1">
@@ -4471,11 +3985,15 @@
           <t>Dinas Tenaga Kerja dan Transmigrasi</t>
         </is>
       </c>
-      <c r="C34" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D34" s="10" t="n">
-        <v>346039368</v>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
@@ -4517,11 +4035,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M34" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N34" s="10" t="n">
-        <v>346039368</v>
+      <c r="M34" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="45" customHeight="1">
@@ -4533,11 +4055,15 @@
           <t>Inspektorat Daerah</t>
         </is>
       </c>
-      <c r="C35" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D35" s="6" t="n">
-        <v>470786500</v>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
@@ -4579,11 +4105,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M35" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="N35" s="6" t="n">
-        <v>470786500</v>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="45" customHeight="1">
@@ -4596,10 +4126,10 @@
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>523391100</v>
+        <v>293964700</v>
       </c>
       <c r="E36" s="8" t="n">
         <v>2</v>
@@ -4630,10 +4160,10 @@
         </is>
       </c>
       <c r="M36" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>301408750</v>
+        <v>71982350</v>
       </c>
     </row>
     <row r="37" ht="45" customHeight="1">
@@ -4646,10 +4176,10 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>835283701</v>
+        <v>471330601</v>
       </c>
       <c r="E37" s="4" t="n">
         <v>6</v>
@@ -4679,11 +4209,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M37" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="N37" s="6" t="n">
-        <v>363953100</v>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="38" ht="45" customHeight="1">
@@ -4692,14 +4226,18 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Arut Utara</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>154997000</v>
+          <t>Kecamatan Kotawaringin Lama</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
@@ -4741,11 +4279,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M38" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" s="10" t="n">
-        <v>154997000</v>
+      <c r="M38" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="45" customHeight="1">
@@ -4754,14 +4296,14 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Kotawaringin Lama</t>
+          <t>Kecamatan Kumai</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>124841500</v>
+        <v>214759000</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
@@ -4804,10 +4346,10 @@
         </is>
       </c>
       <c r="M39" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>124841500</v>
+        <v>214759000</v>
       </c>
     </row>
     <row r="40" ht="45" customHeight="1">
@@ -4816,44 +4358,32 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Kumai</t>
+          <t>Kecamatan Pangkalan Banteng</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>320725524</v>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J40" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>71700000</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>71700000</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="10" t="n">
+        <v>71700000</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v>71700000</v>
       </c>
       <c r="K40" s="11" t="inlineStr">
         <is>
@@ -4865,11 +4395,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M40" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N40" s="10" t="n">
-        <v>320725524</v>
+      <c r="M40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="45" customHeight="1">
@@ -4878,32 +4412,32 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Banteng</t>
+          <t>Laboratorium Kesehatan Daerah</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>137310832</v>
+        <v>340582172</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>71700000</v>
+        <v>340582172</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>71700000</v>
+        <v>68020787</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>71700000</v>
+        <v>68020787</v>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
@@ -4915,11 +4449,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" s="6" t="n">
-        <v>65610832</v>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42" ht="45" customHeight="1">
@@ -4928,7 +4466,7 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Lada</t>
+          <t>Puskesmas Arut Selatan</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
@@ -4998,32 +4536,32 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Laboratorium Kesehatan Daerah</t>
+          <t>Puskesmas Natai Pelingkau</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>403460838</v>
+        <v>348491630</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>340582172</v>
+        <v>153891630</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>68020787</v>
+        <v>53835000</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>68020787</v>
+        <v>53835000</v>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
@@ -5039,7 +4577,7 @@
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>62878666</v>
+        <v>194600000</v>
       </c>
     </row>
     <row r="44" ht="45" customHeight="1">
@@ -5048,14 +4586,18 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Selatan</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D44" s="10" t="n">
-        <v>305850296</v>
+          <t>Puskesmas Riam Durian</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
@@ -5097,11 +4639,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M44" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="N44" s="10" t="n">
-        <v>305850296</v>
+      <c r="M44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="45" customHeight="1">
@@ -5110,44 +4656,32 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Utara</t>
+          <t>Rumah Sakit Kutaringin</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>212926585</v>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>146817603</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>146817603</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>43541637</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>43541637</v>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
@@ -5159,11 +4693,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M45" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N45" s="6" t="n">
-        <v>212926585</v>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="46" ht="45" customHeight="1">
@@ -5172,44 +4710,32 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Ipuh Bangun Jaya</t>
+          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>154700000</v>
-      </c>
-      <c r="E46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>50400000</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>50400000</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>49950000</v>
+      </c>
+      <c r="I46" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>49950000</v>
       </c>
       <c r="K46" s="11" t="inlineStr">
         <is>
@@ -5221,11 +4747,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M46" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="N46" s="10" t="n">
-        <v>154700000</v>
+      <c r="M46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="47" ht="45" customHeight="1">
@@ -5234,14 +4764,14 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Karang Mulya</t>
+          <t>Satuan Polisi Pamong Praja</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>397980729</v>
+        <v>205350000</v>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
@@ -5284,10 +4814,10 @@
         </is>
       </c>
       <c r="M47" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>397980729</v>
+        <v>205350000</v>
       </c>
     </row>
     <row r="48" ht="45" customHeight="1">
@@ -5296,44 +4826,32 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Kotawaringin Lama</t>
+          <t>Sekretariat DPRD</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>50400000</v>
-      </c>
-      <c r="E48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1435364766</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>1285364766</v>
+      </c>
+      <c r="G48" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H48" s="10" t="n">
+        <v>1282534627</v>
+      </c>
+      <c r="I48" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>1226738257</v>
       </c>
       <c r="K48" s="11" t="inlineStr">
         <is>
@@ -5349,7 +4867,7 @@
         <v>1</v>
       </c>
       <c r="N48" s="10" t="n">
-        <v>50400000</v>
+        <v>150000000</v>
       </c>
     </row>
     <row r="49" ht="45" customHeight="1">
@@ -5358,44 +4876,32 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Kumai</t>
+          <t>Sekretariat Daerah</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>749487047</v>
+      </c>
+      <c r="E49" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D49" s="6" t="n">
-        <v>494958640</v>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F49" s="6" t="n">
+        <v>573698247</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>560374825</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>486004825</v>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
@@ -5408,1064 +4914,54 @@
         </is>
       </c>
       <c r="M49" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>494958640</v>
+        <v>175788800</v>
       </c>
     </row>
     <row r="50" ht="45" customHeight="1">
-      <c r="A50" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Kumpai Batu Atas</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D50" s="10" t="n">
-        <v>189350000</v>
-      </c>
-      <c r="E50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M50" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="N50" s="10" t="n">
-        <v>189350000</v>
-      </c>
-    </row>
-    <row r="51" ht="45" customHeight="1">
-      <c r="A51" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Madurejo</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D51" s="6" t="n">
-        <v>235342500</v>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M51" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N51" s="6" t="n">
-        <v>235342500</v>
-      </c>
-    </row>
-    <row r="52" ht="45" customHeight="1">
-      <c r="A52" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Mendawai</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D52" s="10" t="n">
-        <v>141393225</v>
-      </c>
-      <c r="E52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M52" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="N52" s="10" t="n">
-        <v>141393225</v>
-      </c>
-    </row>
-    <row r="53" ht="45" customHeight="1">
-      <c r="A53" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Natai Pelingkau</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D53" s="6" t="n">
-        <v>348491630</v>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="6" t="n">
-        <v>153891630</v>
-      </c>
-      <c r="G53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" s="6" t="n">
-        <v>53835000</v>
-      </c>
-      <c r="I53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="6" t="n">
-        <v>53835000</v>
-      </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N53" s="6" t="n">
-        <v>194600000</v>
-      </c>
-    </row>
-    <row r="54" ht="45" customHeight="1">
-      <c r="A54" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Pandu Sanjaya</t>
-        </is>
-      </c>
-      <c r="C54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="45" customHeight="1">
-      <c r="A55" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Pangkalan Lada</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D55" s="6" t="n">
-        <v>189000000</v>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M55" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N55" s="6" t="n">
-        <v>189000000</v>
-      </c>
-    </row>
-    <row r="56" ht="45" customHeight="1">
-      <c r="A56" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Riam Durian</t>
-        </is>
-      </c>
-      <c r="C56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="45" customHeight="1">
-      <c r="A57" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Runtu</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" s="6" t="n">
-        <v>143150000</v>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M57" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N57" s="6" t="n">
-        <v>143150000</v>
-      </c>
-    </row>
-    <row r="58" ht="45" customHeight="1">
-      <c r="A58" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Sambi</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" s="10" t="n">
-        <v>149292000</v>
-      </c>
-      <c r="E58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M58" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N58" s="10" t="n">
-        <v>149292000</v>
-      </c>
-    </row>
-    <row r="59" ht="45" customHeight="1">
-      <c r="A59" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Semanggang</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D59" s="6" t="n">
-        <v>275450000</v>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M59" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N59" s="6" t="n">
-        <v>275450000</v>
-      </c>
-    </row>
-    <row r="60" ht="45" customHeight="1">
-      <c r="A60" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Sungai Rangit</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" s="10" t="n">
-        <v>66272893</v>
-      </c>
-      <c r="E60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M60" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N60" s="10" t="n">
-        <v>66272893</v>
-      </c>
-    </row>
-    <row r="61" ht="45" customHeight="1">
-      <c r="A61" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Teluk Bogam</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D61" s="6" t="n">
-        <v>156525300</v>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M61" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N61" s="6" t="n">
-        <v>156525300</v>
-      </c>
-    </row>
-    <row r="62" ht="45" customHeight="1">
-      <c r="A62" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Kutaringin</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D62" s="10" t="n">
-        <v>647501699</v>
-      </c>
-      <c r="E62" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" s="10" t="n">
-        <v>146817603</v>
-      </c>
-      <c r="G62" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H62" s="10" t="n">
-        <v>43541637</v>
-      </c>
-      <c r="I62" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="10" t="n">
-        <v>43541637</v>
-      </c>
-      <c r="K62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M62" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="N62" s="10" t="n">
-        <v>500684096</v>
-      </c>
-    </row>
-    <row r="63" ht="45" customHeight="1">
-      <c r="A63" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="D63" s="6" t="n">
-        <v>3441387498</v>
-      </c>
-      <c r="E63" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="6" t="n">
-        <v>50400000</v>
-      </c>
-      <c r="G63" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H63" s="6" t="n">
-        <v>49950000</v>
-      </c>
-      <c r="I63" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="6" t="n">
-        <v>49950000</v>
-      </c>
-      <c r="K63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M63" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="N63" s="6" t="n">
-        <v>3390987498</v>
-      </c>
-    </row>
-    <row r="64" ht="45" customHeight="1">
-      <c r="A64" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>Satuan Polisi Pamong Praja</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D64" s="10" t="n">
-        <v>463002876</v>
-      </c>
-      <c r="E64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M64" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N64" s="10" t="n">
-        <v>463002876</v>
-      </c>
-    </row>
-    <row r="65" ht="45" customHeight="1">
-      <c r="A65" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>Sekretariat DPRD</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D65" s="6" t="n">
-        <v>2559430816</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="F65" s="6" t="n">
-        <v>1285364766</v>
-      </c>
-      <c r="G65" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="H65" s="6" t="n">
-        <v>1282534627</v>
-      </c>
-      <c r="I65" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="J65" s="6" t="n">
-        <v>1226738257</v>
-      </c>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M65" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N65" s="6" t="n">
-        <v>1274066050</v>
-      </c>
-    </row>
-    <row r="66" ht="45" customHeight="1">
-      <c r="A66" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>Sekretariat Daerah</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="D66" s="10" t="n">
-        <v>2995755132</v>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F66" s="10" t="n">
-        <v>573698247</v>
-      </c>
-      <c r="G66" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H66" s="10" t="n">
-        <v>560374825</v>
-      </c>
-      <c r="I66" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J66" s="10" t="n">
-        <v>486004825</v>
-      </c>
-      <c r="K66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M66" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="N66" s="10" t="n">
-        <v>2422056885</v>
-      </c>
-    </row>
-    <row r="67" ht="45" customHeight="1">
-      <c r="A67" s="2" t="inlineStr"/>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>TOTAL KESELURUHAN</t>
         </is>
       </c>
-      <c r="C67" s="12" t="n">
-        <v>799</v>
-      </c>
-      <c r="D67" s="13" t="n">
-        <v>94875567618</v>
-      </c>
-      <c r="E67" s="12" t="n">
+      <c r="C50" s="12" t="n">
+        <v>484</v>
+      </c>
+      <c r="D50" s="13" t="n">
+        <v>62169318995</v>
+      </c>
+      <c r="E50" s="12" t="n">
         <v>422</v>
       </c>
-      <c r="F67" s="13" t="n">
+      <c r="F50" s="13" t="n">
         <v>53916470304</v>
       </c>
-      <c r="G67" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>422</v>
       </c>
-      <c r="H67" s="13" t="n">
+      <c r="H50" s="13" t="n">
         <v>52071815180.4</v>
       </c>
-      <c r="I67" s="12" t="n">
+      <c r="I50" s="12" t="n">
         <v>207</v>
       </c>
-      <c r="J67" s="13" t="n">
+      <c r="J50" s="13" t="n">
         <v>24695276382</v>
       </c>
-      <c r="K67" s="12" t="n">
+      <c r="K50" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L67" s="13" t="n">
+      <c r="L50" s="13" t="n">
         <v>764123653</v>
       </c>
-      <c r="M67" s="12" t="n">
-        <v>377</v>
-      </c>
-      <c r="N67" s="13" t="n">
-        <v>40959097314</v>
+      <c r="M50" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="N50" s="13" t="n">
+        <v>8252848691</v>
       </c>
     </row>
   </sheetData>
@@ -6497,7 +4993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6898,11 +5394,15 @@
           <t>Badan Keuangan dan Aset Daerah</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>206878992</v>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -6944,11 +5444,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>206878992</v>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
@@ -7031,10 +5535,10 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1344967600</v>
+        <v>1128517600</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>1</v>
@@ -7065,10 +5569,10 @@
         </is>
       </c>
       <c r="M13" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>1128517600</v>
+        <v>912067600</v>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
@@ -7080,11 +5584,15 @@
           <t>Badan Perencanaan Pembangunan, Riset dan Inovasi Daerah</t>
         </is>
       </c>
-      <c r="C14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>217952667</v>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
@@ -7126,11 +5634,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" s="10" t="n">
-        <v>217952667</v>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
@@ -7142,11 +5654,15 @@
           <t>Dinas Kepemudaan dan Olahraga</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>658884360</v>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -7188,11 +5704,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" s="6" t="n">
-        <v>658884360</v>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
@@ -7255,10 +5775,10 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>50117240767</v>
+        <v>49112440318</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>32</v>
@@ -7284,11 +5804,15 @@
       <c r="L17" s="6" t="n">
         <v>1101458974</v>
       </c>
-      <c r="M17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N17" s="6" t="n">
-        <v>1004800449</v>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1">
@@ -7371,10 +5895,10 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>6129521900</v>
+        <v>3459514800</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>4</v>
@@ -7404,11 +5928,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M19" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N19" s="6" t="n">
-        <v>2670007100</v>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="45" customHeight="1">
@@ -7475,10 +6003,10 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>35948239265</v>
+        <v>33663796833</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>42</v>
@@ -7509,10 +6037,10 @@
         </is>
       </c>
       <c r="M21" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>2601247532</v>
+        <v>316805100</v>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
@@ -7525,10 +6053,10 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>1366776000</v>
+        <v>1086690000</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>2</v>
@@ -7558,11 +6086,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M22" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" s="10" t="n">
-        <v>280086000</v>
+      <c r="M22" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1">
@@ -7574,11 +6106,15 @@
           <t>Dinas Pemberdayaan Masyarakat dan Desa</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>914760000</v>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -7620,11 +6156,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>914760000</v>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1">
@@ -7637,10 +6177,10 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>795600000</v>
+        <v>483600000</v>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
@@ -7683,10 +6223,10 @@
         </is>
       </c>
       <c r="M24" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N24" s="10" t="n">
-        <v>795600000</v>
+        <v>483600000</v>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
@@ -7698,11 +6238,15 @@
           <t>Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>205076880</v>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -7744,11 +6288,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" s="6" t="n">
-        <v>205076880</v>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
@@ -7761,10 +6309,10 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>2966457340</v>
+        <v>1969342000</v>
       </c>
       <c r="E26" s="8" t="n">
         <v>3</v>
@@ -7795,10 +6343,10 @@
         </is>
       </c>
       <c r="M26" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N26" s="10" t="n">
-        <v>2253119340</v>
+        <v>1256004000</v>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1">
@@ -7811,10 +6359,10 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>729033456</v>
+        <v>201600000</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>1</v>
@@ -7844,11 +6392,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M27" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N27" s="6" t="n">
-        <v>527433456</v>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
@@ -7861,10 +6413,10 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>2208956507</v>
+        <v>1280399846</v>
       </c>
       <c r="E28" s="8" t="n">
         <v>4</v>
@@ -7895,10 +6447,10 @@
         </is>
       </c>
       <c r="M28" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N28" s="10" t="n">
-        <v>1146542013</v>
+        <v>217985352</v>
       </c>
     </row>
     <row r="29" ht="45" customHeight="1">
@@ -7911,10 +6463,10 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>5338130896</v>
+        <v>4037584000</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>4</v>
@@ -7940,11 +6492,15 @@
       <c r="L29" s="6" t="n">
         <v>436796630</v>
       </c>
-      <c r="M29" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N29" s="6" t="n">
-        <v>1300546896</v>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
@@ -8027,10 +6583,10 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>3813601480</v>
+        <v>2620841480</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>7</v>
@@ -8061,10 +6617,10 @@
         </is>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>1437760000</v>
+        <v>245000000</v>
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
@@ -8077,10 +6633,10 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>3639664785</v>
+        <v>2516796000</v>
       </c>
       <c r="E32" s="8" t="n">
         <v>2</v>
@@ -8111,10 +6667,10 @@
         </is>
       </c>
       <c r="M32" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N32" s="10" t="n">
-        <v>3093962385</v>
+        <v>1971093600</v>
       </c>
     </row>
     <row r="33" ht="45" customHeight="1">
@@ -8401,18 +6957,14 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Arut Utara</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Kecamatan Kotawaringin Lama</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>440899992</v>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
@@ -8454,15 +7006,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M38" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N38" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M38" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" s="10" t="n">
+        <v>440899992</v>
       </c>
     </row>
     <row r="39" ht="45" customHeight="1">
@@ -8471,14 +7019,18 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Kotawaringin Lama</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="6" t="n">
-        <v>440899992</v>
+          <t>Kecamatan Kumai</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
@@ -8520,11 +7072,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N39" s="6" t="n">
-        <v>440899992</v>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="45" customHeight="1">
@@ -8533,7 +7089,7 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Kumai</t>
+          <t>Kecamatan Pangkalan Banteng</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
@@ -8603,7 +7159,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Banteng</t>
+          <t>Laboratorium Kesehatan Daerah</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -8673,7 +7229,7 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Lada</t>
+          <t>Puskesmas Arut Selatan</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
@@ -8743,14 +7299,18 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Laboratorium Kesehatan Daerah</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D43" s="6" t="n">
-        <v>1937370950</v>
+          <t>Puskesmas Natai Pelingkau</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
@@ -8792,11 +7352,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M43" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N43" s="6" t="n">
-        <v>1937370950</v>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44" ht="45" customHeight="1">
@@ -8805,14 +7369,18 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Selatan</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="10" t="n">
-        <v>1032445697</v>
+          <t>Puskesmas Riam Durian</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
@@ -8854,11 +7422,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M44" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N44" s="10" t="n">
-        <v>1032445697</v>
+      <c r="M44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="45" customHeight="1">
@@ -8867,14 +7439,18 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Utara</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="6" t="n">
-        <v>456516000</v>
+          <t>Rumah Sakit Kutaringin</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
@@ -8916,11 +7492,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N45" s="6" t="n">
-        <v>456516000</v>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="46" ht="45" customHeight="1">
@@ -8929,58 +7509,38 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Ipuh Bangun Jaya</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>7812519000</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>7812519000</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>2779934202</v>
+      </c>
+      <c r="I46" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>2779934202</v>
+      </c>
+      <c r="K46" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L46" s="10" t="n">
+        <v>64551162</v>
       </c>
       <c r="M46" s="11" t="inlineStr">
         <is>
@@ -8999,7 +7559,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Karang Mulya</t>
+          <t>Satuan Polisi Pamong Praja</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
@@ -9069,48 +7629,32 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Kotawaringin Lama</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J48" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Sekretariat DPRD</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="10" t="n">
+        <v>218268000</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>218268000</v>
+      </c>
+      <c r="G48" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="10" t="n">
+        <v>185076000</v>
+      </c>
+      <c r="I48" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>185076000</v>
       </c>
       <c r="K48" s="11" t="inlineStr">
         <is>
@@ -9139,44 +7683,32 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Kumai</t>
+          <t>Sekretariat Daerah</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>223700000</v>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2944207800</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>2944207800</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>2058441500</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>2058441500</v>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
@@ -9188,1173 +7720,59 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N49" s="6" t="n">
-        <v>223700000</v>
+      <c r="M49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50" ht="45" customHeight="1">
-      <c r="A50" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Kumpai Batu Atas</t>
-        </is>
-      </c>
-      <c r="C50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="45" customHeight="1">
-      <c r="A51" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Madurejo</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="45" customHeight="1">
-      <c r="A52" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Mendawai</t>
-        </is>
-      </c>
-      <c r="C52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="45" customHeight="1">
-      <c r="A53" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Natai Pelingkau</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="45" customHeight="1">
-      <c r="A54" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Pandu Sanjaya</t>
-        </is>
-      </c>
-      <c r="C54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="45" customHeight="1">
-      <c r="A55" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Pangkalan Lada</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="45" customHeight="1">
-      <c r="A56" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Riam Durian</t>
-        </is>
-      </c>
-      <c r="C56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="45" customHeight="1">
-      <c r="A57" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Runtu</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="45" customHeight="1">
-      <c r="A58" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Sambi</t>
-        </is>
-      </c>
-      <c r="C58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="45" customHeight="1">
-      <c r="A59" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Semanggang</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="45" customHeight="1">
-      <c r="A60" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Sungai Rangit</t>
-        </is>
-      </c>
-      <c r="C60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="45" customHeight="1">
-      <c r="A61" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Teluk Bogam</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="45" customHeight="1">
-      <c r="A62" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Kutaringin</t>
-        </is>
-      </c>
-      <c r="C62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="45" customHeight="1">
-      <c r="A63" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="n">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL KESELURUHAN</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="D50" s="13" t="n">
+        <v>124989099969</v>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>124</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>116436609400</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>124</v>
+      </c>
+      <c r="H50" s="13" t="n">
+        <v>57171516936</v>
+      </c>
+      <c r="I50" s="12" t="n">
+        <v>113</v>
+      </c>
+      <c r="J50" s="13" t="n">
+        <v>55081222936</v>
+      </c>
+      <c r="K50" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="D63" s="6" t="n">
-        <v>15827645837</v>
-      </c>
-      <c r="E63" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="F63" s="6" t="n">
-        <v>7812519000</v>
-      </c>
-      <c r="G63" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H63" s="6" t="n">
-        <v>2779934202</v>
-      </c>
-      <c r="I63" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="J63" s="6" t="n">
-        <v>2779934202</v>
-      </c>
-      <c r="K63" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L63" s="6" t="n">
-        <v>64551162</v>
-      </c>
-      <c r="M63" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="N63" s="6" t="n">
-        <v>8015126837</v>
-      </c>
-    </row>
-    <row r="64" ht="45" customHeight="1">
-      <c r="A64" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>Satuan Polisi Pamong Praja</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" s="10" t="n">
-        <v>211404000</v>
-      </c>
-      <c r="E64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M64" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N64" s="10" t="n">
-        <v>211404000</v>
-      </c>
-    </row>
-    <row r="65" ht="45" customHeight="1">
-      <c r="A65" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>Sekretariat DPRD</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D65" s="6" t="n">
-        <v>5031291001</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="6" t="n">
-        <v>218268000</v>
-      </c>
-      <c r="G65" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H65" s="6" t="n">
-        <v>185076000</v>
-      </c>
-      <c r="I65" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="6" t="n">
-        <v>185076000</v>
-      </c>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M65" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="N65" s="6" t="n">
-        <v>4813023001</v>
-      </c>
-    </row>
-    <row r="66" ht="45" customHeight="1">
-      <c r="A66" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>Sekretariat Daerah</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="D66" s="10" t="n">
-        <v>7626623356</v>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F66" s="10" t="n">
-        <v>2944207800</v>
-      </c>
-      <c r="G66" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H66" s="10" t="n">
-        <v>2058441500</v>
-      </c>
-      <c r="I66" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J66" s="10" t="n">
-        <v>2058441500</v>
-      </c>
-      <c r="K66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M66" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="N66" s="10" t="n">
-        <v>4682415556</v>
-      </c>
-    </row>
-    <row r="67" ht="45" customHeight="1">
-      <c r="A67" s="2" t="inlineStr"/>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL KESELURUHAN</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="n">
-        <v>215</v>
-      </c>
-      <c r="D67" s="13" t="n">
-        <v>161401722028</v>
-      </c>
-      <c r="E67" s="12" t="n">
-        <v>124</v>
-      </c>
-      <c r="F67" s="13" t="n">
-        <v>116436609400</v>
-      </c>
-      <c r="G67" s="12" t="n">
-        <v>124</v>
-      </c>
-      <c r="H67" s="13" t="n">
-        <v>57171516936</v>
-      </c>
-      <c r="I67" s="12" t="n">
-        <v>113</v>
-      </c>
-      <c r="J67" s="13" t="n">
-        <v>55081222936</v>
-      </c>
-      <c r="K67" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="L67" s="13" t="n">
+      <c r="L50" s="13" t="n">
         <v>2094471498</v>
       </c>
-      <c r="M67" s="12" t="n">
-        <v>91</v>
-      </c>
-      <c r="N67" s="13" t="n">
-        <v>44965112628</v>
+      <c r="M50" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="N50" s="13" t="n">
+        <v>8552490569</v>
       </c>
     </row>
   </sheetData>
@@ -10386,7 +7804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11860,10 +9278,10 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>8328788319</v>
+        <v>5040000000</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>1</v>
@@ -11893,11 +9311,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" s="6" t="n">
-        <v>3288788319</v>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
@@ -12103,11 +9525,15 @@
           <t>Dinas Pertanian</t>
         </is>
       </c>
-      <c r="C31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="6" t="n">
-        <v>2509875000</v>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
@@ -12149,11 +9575,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" s="6" t="n">
-        <v>2509875000</v>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
@@ -12582,7 +10012,7 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Arut Utara</t>
+          <t>Kecamatan Kotawaringin Lama</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
@@ -12652,7 +10082,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Kotawaringin Lama</t>
+          <t>Kecamatan Kumai</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -12722,7 +10152,7 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Kumai</t>
+          <t>Kecamatan Pangkalan Banteng</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
@@ -12792,7 +10222,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Banteng</t>
+          <t>Laboratorium Kesehatan Daerah</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -12862,7 +10292,7 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Kecamatan Pangkalan Lada</t>
+          <t>Puskesmas Arut Selatan</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
@@ -12932,7 +10362,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Laboratorium Kesehatan Daerah</t>
+          <t>Puskesmas Natai Pelingkau</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
@@ -13002,7 +10432,7 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Selatan</t>
+          <t>Puskesmas Riam Durian</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
@@ -13072,7 +10502,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Arut Utara</t>
+          <t>Rumah Sakit Kutaringin</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -13142,48 +10572,32 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Ipuh Bangun Jaya</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>73360000000</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>73360000000</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>8116023274</v>
+      </c>
+      <c r="I46" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>8116023274</v>
       </c>
       <c r="K46" s="11" t="inlineStr">
         <is>
@@ -13212,7 +10626,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Karang Mulya</t>
+          <t>Satuan Polisi Pamong Praja</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
@@ -13282,7 +10696,7 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Puskesmas Kotawaringin Lama</t>
+          <t>Sekretariat DPRD</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
@@ -13352,7 +10766,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Puskesmas Kumai</t>
+          <t>Sekretariat Daerah</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
@@ -13417,1221 +10831,51 @@
       </c>
     </row>
     <row r="50" ht="45" customHeight="1">
-      <c r="A50" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Kumpai Batu Atas</t>
-        </is>
-      </c>
-      <c r="C50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N50" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="45" customHeight="1">
-      <c r="A51" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Madurejo</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="45" customHeight="1">
-      <c r="A52" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Mendawai</t>
-        </is>
-      </c>
-      <c r="C52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N52" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="45" customHeight="1">
-      <c r="A53" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Natai Pelingkau</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="45" customHeight="1">
-      <c r="A54" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Pandu Sanjaya</t>
-        </is>
-      </c>
-      <c r="C54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N54" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="45" customHeight="1">
-      <c r="A55" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Pangkalan Lada</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="45" customHeight="1">
-      <c r="A56" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Riam Durian</t>
-        </is>
-      </c>
-      <c r="C56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="45" customHeight="1">
-      <c r="A57" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Runtu</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="45" customHeight="1">
-      <c r="A58" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Sambi</t>
-        </is>
-      </c>
-      <c r="C58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="45" customHeight="1">
-      <c r="A59" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Semanggang</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="45" customHeight="1">
-      <c r="A60" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>Puskesmas Sungai Rangit</t>
-        </is>
-      </c>
-      <c r="C60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N60" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="45" customHeight="1">
-      <c r="A61" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>Puskesmas Teluk Bogam</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="45" customHeight="1">
-      <c r="A62" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Kutaringin</t>
-        </is>
-      </c>
-      <c r="C62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N62" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="45" customHeight="1">
-      <c r="A63" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>Rumah Sakit Umum Daerah Sultan Imanuddin</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D63" s="6" t="n">
-        <v>135106211738</v>
-      </c>
-      <c r="E63" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="F63" s="6" t="n">
-        <v>73360000000</v>
-      </c>
-      <c r="G63" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="H63" s="6" t="n">
-        <v>8116023274</v>
-      </c>
-      <c r="I63" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J63" s="6" t="n">
-        <v>8116023274</v>
-      </c>
-      <c r="K63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M63" s="4" t="n">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL KESELURUHAN</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="D50" s="13" t="n">
+        <v>187157560800</v>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>137115370800</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="H50" s="13" t="n">
+        <v>71014601008.97</v>
+      </c>
+      <c r="I50" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J50" s="13" t="n">
+        <v>71014601008.97</v>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M50" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N63" s="6" t="n">
-        <v>61746211738</v>
-      </c>
-    </row>
-    <row r="64" ht="45" customHeight="1">
-      <c r="A64" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>Satuan Polisi Pamong Praja</t>
-        </is>
-      </c>
-      <c r="C64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N64" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="45" customHeight="1">
-      <c r="A65" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>Sekretariat DPRD</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="45" customHeight="1">
-      <c r="A66" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>Sekretariat Daerah</t>
-        </is>
-      </c>
-      <c r="C66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N66" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="45" customHeight="1">
-      <c r="A67" s="2" t="inlineStr"/>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL KESELURUHAN</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="D67" s="13" t="n">
-        <v>254702435857</v>
-      </c>
-      <c r="E67" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="F67" s="13" t="n">
-        <v>137115370800</v>
-      </c>
-      <c r="G67" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="H67" s="13" t="n">
-        <v>71014601008.97</v>
-      </c>
-      <c r="I67" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="J67" s="13" t="n">
-        <v>71014601008.97</v>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M67" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="N67" s="13" t="n">
-        <v>117587065057</v>
+      <c r="N50" s="13" t="n">
+        <v>50042190000</v>
       </c>
     </row>
   </sheetData>
